--- a/reports/summary/summary_pipeline.xlsx
+++ b/reports/summary/summary_pipeline.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -755,10 +755,9 @@
       <c r="G4" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" t="n">
         <v>46.04</v>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
         <v>0</v>
       </c>
@@ -802,6 +801,86 @@
       <c r="V4" t="inlineStr">
         <is>
           <t>run_20260808_053444</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-08 11:54:33</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>run_20260808_115430</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>laptop</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>49.77</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>_labels_test.csv</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>10</v>
+      </c>
+      <c r="R5" t="b">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>8dbb7c0</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>run_20260808_115430</t>
         </is>
       </c>
     </row>

--- a/reports/summary/summary_pipeline.xlsx
+++ b/reports/summary/summary_pipeline.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -837,7 +837,6 @@
       <c r="H5" s="2" t="n">
         <v>49.77</v>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
         <v>0</v>
       </c>
@@ -881,6 +880,82 @@
       <c r="V5" t="inlineStr">
         <is>
           <t>run_20260808_115430</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-08 13:47:53</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>run_20260808_134739</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>webcam</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>laptop</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>172</v>
+      </c>
+      <c r="G6" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>18.69</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>walking</t>
+        </is>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>10</v>
+      </c>
+      <c r="R6" t="b">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>26a5720</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>run_20260808_134739</t>
         </is>
       </c>
     </row>
